--- a/output/quickfixclose1_portfolio_daily.xlsx
+++ b/output/quickfixclose1_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$185</f>
+              <f>'equity_curve'!$A$2:$A$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$185</f>
+              <f>'equity_curve'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-30</t>
+          <t>2025-12-18 -&gt; 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5477,6 +5477,26 @@
           <t>NY_Natural_Gas_Futures exit_close (+12,513)</t>
         </is>
       </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>531970.55</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>531970.55</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixclose1_portfolio_daily.xlsx
+++ b/output/quickfixclose1_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>42% of trading days</t>
+          <t>41% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5497,6 +5497,46 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>531970.55</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>531970.55</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>531970.55</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>531970.55</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixclose1_portfolio_daily.xlsx
+++ b/output/quickfixclose1_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>531,970.55</t>
+          <t>553,754.96</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+431.97%</t>
+          <t>+453.75%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>550,998  (+451.00%)</t>
+          <t>573,612  (+473.61%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,343  (19.0 pts of return)</t>
+          <t>7,392  (19.9 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>93.5x</t>
+          <t>98.2x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+3.52R  (best +16.18R)</t>
+          <t>+3.42R  (best +16.18R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8,150  (+3.52%)</t>
+          <t>8,108  (+3.42%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5538,6 +5538,62 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>531970.55</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>15800.06</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>516170.49</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 5,320); Nasdaq_100_E_mini short (risk 5,267); S_P_500_E_mini short (risk 5,214)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>553754.96</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>553754.96</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 5,162)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini exit_close (+11,757); NY_Platinum_Futures exit_close (+5,818); S_P_500_E_mini exit_close (+4,218)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5550,7 +5606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10327,6 +10383,202 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>969893.92</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>13481.53</v>
+      </c>
+      <c r="K94" s="6" t="n">
+        <v>14745.49</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>1014295</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>956412.39</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>13294.13</v>
+      </c>
+      <c r="K95" s="6" t="n">
+        <v>29677.68</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>999549.5</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>943118.26</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>13109.34</v>
+      </c>
+      <c r="K96" s="6" t="n">
+        <v>10605.16</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>1024900.15</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>930008.92</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>12927.12</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>969871.8199999999</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixclose1_portfolio_daily.xlsx
+++ b/output/quickfixclose1_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>553,754.96</t>
+          <t>548,510.52</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+453.75%</t>
+          <t>+448.51%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>573,612  (+473.61%)</t>
+          <t>568,266  (+468.27%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,392  (19.9 pts of return)</t>
+          <t>7,475  (19.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>98.2x</t>
+          <t>97.1x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,783  (-1.04%)</t>
+          <t>-1,886  (-1.04%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>41% of trading days</t>
+          <t>42% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5571,26 +5571,58 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>553754.96</v>
+        <v>553763.78</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>5161.7</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>548602.0699999999</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 5,162)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini exit_close (+11,757); NY_Platinum_Futures exit_close (+5,818); S_P_500_E_mini exit_close (+4,218)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>548510.52</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>553754.96</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 5,162)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini exit_close (+11,757); NY_Platinum_Futures exit_close (+5,818); S_P_500_E_mini exit_close (+4,218)</t>
+      <c r="D191" s="5" t="n">
+        <v>548510.52</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 5,486); NY_Palladium_Futures short (risk 5,431); NY_Platinum_Futures short (risk 5,377)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-5,197); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5619,7 +5651,7 @@
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
@@ -10426,7 +10458,7 @@
         <v>14745.49</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>1014295</v>
+        <v>1014317.09</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -10477,7 +10509,7 @@
         <v>29677.68</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>999549.5</v>
+        <v>999571.6</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -10528,7 +10560,7 @@
         <v>10605.16</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>1024900.15</v>
+        <v>1024922.25</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -10552,14 +10584,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G97" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>930008.92</v>
@@ -10568,12 +10608,141 @@
         <v>12927.12</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>-22.1</v>
+        <v>-13015.51</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>969871.8199999999</v>
+        <v>1011906.74</v>
       </c>
       <c r="M97" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>1011995.13</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>14066.73</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>-38.02</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>1011868.72</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>997928.39</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>13871.2</v>
+      </c>
+      <c r="K99" s="7" t="n">
+        <v>-54.4</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>1011814.32</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>984057.1899999999</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>13678.39</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>-51.23</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>1011763.09</v>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
